--- a/01_Reporting_Suite/Reports/2026-08-05/Pages/Flame_Off_Site_Plant_Utilisation_05Aug2026.xlsx
+++ b/01_Reporting_Suite/Reports/2026-08-05/Pages/Flame_Off_Site_Plant_Utilisation_05Aug2026.xlsx
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>21</v>
@@ -1017,7 +1017,7 @@
         <v>413.9999999999999</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>1552.499999999999</v>
+        <v>1655.999999999998</v>
       </c>
       <c r="S10" s="7" t="n">
         <v>103.5</v>
@@ -1261,7 +1261,7 @@
         <v>128</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>480</v>
+        <v>512.0000000000002</v>
       </c>
       <c r="S11" s="7" t="n">
         <v>32</v>
@@ -1505,7 +1505,7 @@
         <v>33.28</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>124.8</v>
+        <v>133.12</v>
       </c>
       <c r="S12" s="7" t="n">
         <v>8.32</v>
@@ -1749,7 +1749,7 @@
         <v>33.28</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>124.8</v>
+        <v>133.12</v>
       </c>
       <c r="S13" s="7" t="n">
         <v>8.32</v>
@@ -1993,7 +1993,7 @@
         <v>291.2</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>1092.000000000001</v>
+        <v>1164.8</v>
       </c>
       <c r="S14" s="7" t="n">
         <v>72.8</v>
@@ -2198,11 +2198,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Available for Hire</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
@@ -2442,11 +2438,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Available for Hire</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
@@ -2686,11 +2678,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Available for Hire</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
@@ -2930,11 +2918,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Available for Hire</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
@@ -3174,11 +3158,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Available for Hire</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
@@ -3674,11 +3654,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>On Hire</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>02/08/2026</t>
@@ -3969,7 +3945,7 @@
         <v>53.92</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>202.2</v>
+        <v>215.68</v>
       </c>
       <c r="S22" s="7" t="n">
         <v>13.48</v>
@@ -10173,7 +10149,7 @@
         <v>19.4</v>
       </c>
       <c r="R47" s="7" t="n">
-        <v>58.2</v>
+        <v>62.08</v>
       </c>
       <c r="S47" s="7" t="n">
         <v>3.88</v>
@@ -18321,7 +18297,7 @@
         <v>233.3</v>
       </c>
       <c r="R80" s="7" t="n">
-        <v>606.5799999999999</v>
+        <v>653.24</v>
       </c>
       <c r="S80" s="7" t="n">
         <v>46.66</v>
@@ -20576,7 +20552,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>On Hire</t>
+          <t>Available for Hire</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -20586,20 +20562,20 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="6" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -20612,10 +20588,10 @@
         </is>
       </c>
       <c r="O89" s="7" t="n">
-        <v>1600</v>
+        <v>1440</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="Q89" s="7" t="n">
         <v>1760</v>
@@ -20628,7 +20604,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>USED: DGH Engineering</t>
+          <t>SITE PLANT</t>
         </is>
       </c>
       <c r="U89" t="n">
@@ -20639,7 +20615,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>BOSCH REXROTH, CEMENT AUSTRALIA HOLDINGS PTY LTD, DGH Engineering, Dark Knight Engineering</t>
+          <t>BOSCH REXROTH, CEMENT AUSTRALIA HOLDINGS PTY LTD, Dark Knight Engineering, VEOLIA</t>
         </is>
       </c>
       <c r="X89" s="8" t="inlineStr">
@@ -20762,9 +20738,9 @@
           <t>USED: Dark Knight Engineering</t>
         </is>
       </c>
-      <c r="AV89" s="11" t="inlineStr">
-        <is>
-          <t>USED: DGH Engineering</t>
+      <c r="AV89" s="10" t="inlineStr">
+        <is>
+          <t>SITE PLANT</t>
         </is>
       </c>
       <c r="AW89" s="8" t="inlineStr">
@@ -20832,7 +20808,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Available for Hire</t>
+          <t>On Hire</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -20842,11 +20818,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
@@ -20855,7 +20831,7 @@
         <v>0</v>
       </c>
       <c r="L90" s="6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -20868,23 +20844,23 @@
         </is>
       </c>
       <c r="O90" s="7" t="n">
-        <v>917.7</v>
+        <v>978.88</v>
       </c>
       <c r="P90" s="7" t="n">
         <v>61.18</v>
       </c>
       <c r="Q90" s="7" t="n">
-        <v>305.9</v>
+        <v>244.72</v>
       </c>
       <c r="R90" s="7" t="n">
-        <v>61.18</v>
+        <v>122.36</v>
       </c>
       <c r="S90" s="7" t="n">
         <v>61.18</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>OFF / NOT SEEN</t>
+          <t>SITE PLANT</t>
         </is>
       </c>
       <c r="U90" t="n">
@@ -20895,7 +20871,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>DGH Engineering, HIGH RISK SOLUTIONS</t>
+          <t>DGH Engineering, Dark Knight Engineering, HIGH RISK SOLUTIONS</t>
         </is>
       </c>
       <c r="X90" s="8" t="inlineStr">
@@ -21013,14 +20989,14 @@
           <t>USED: DGH Engineering</t>
         </is>
       </c>
-      <c r="AU90" s="10" t="inlineStr">
-        <is>
-          <t>SITE PLANT</t>
-        </is>
-      </c>
-      <c r="AV90" s="9" t="inlineStr">
-        <is>
-          <t>OFF / NOT SEEN</t>
+      <c r="AU90" s="11" t="inlineStr">
+        <is>
+          <t>USED: Dark Knight Engineering</t>
+        </is>
+      </c>
+      <c r="AV90" s="10" t="inlineStr">
+        <is>
+          <t>SITE PLANT</t>
         </is>
       </c>
       <c r="AW90" s="8" t="inlineStr">
@@ -21407,7 +21383,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>CEMENT AUSTRALIA HOLDINGS PTY LTD</t>
+          <t>BOSCH REXROTH, CEMENT AUSTRALIA HOLDINGS PTY LTD</t>
         </is>
       </c>
       <c r="X92" s="8" t="inlineStr">
@@ -21527,7 +21503,7 @@
       </c>
       <c r="AU92" s="11" t="inlineStr">
         <is>
-          <t>USED: CEMENT AUSTRALIA HOLDINGS PTY LTD</t>
+          <t>USED: BOSCH REXROTH</t>
         </is>
       </c>
       <c r="AV92" s="11" t="inlineStr">
@@ -21875,7 +21851,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SITEIQ</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -21893,7 +21869,7 @@
         <v>123.5</v>
       </c>
       <c r="R94" s="7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S94" s="7" t="n">
         <v>6.5</v>
@@ -23102,11 +23078,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>On Hire</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>01/08/2026</t>
@@ -25409,7 +25381,7 @@
         <v>106.72</v>
       </c>
       <c r="R108" s="7" t="n">
-        <v>400.2</v>
+        <v>426.88</v>
       </c>
       <c r="S108" s="7" t="n">
         <v>26.68</v>
@@ -26602,11 +26574,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>On Hire</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>25/07/2026</t>
@@ -26614,20 +26582,20 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J113" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="6" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -26640,23 +26608,23 @@
         </is>
       </c>
       <c r="O113" s="7" t="n">
-        <v>1016</v>
+        <v>1143</v>
       </c>
       <c r="P113" s="7" t="n">
-        <v>1143</v>
+        <v>889</v>
       </c>
       <c r="Q113" s="7" t="n">
-        <v>508</v>
+        <v>635</v>
       </c>
       <c r="R113" s="7" t="n">
-        <v>1143</v>
+        <v>1270</v>
       </c>
       <c r="S113" s="7" t="n">
         <v>127</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>SITE PLANT</t>
+          <t>OFF / NOT SEEN</t>
         </is>
       </c>
       <c r="U113" t="n">
@@ -26667,7 +26635,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>HIGH RISK SOLUTIONS, XTREME ENGINEERING</t>
+          <t>CEMENT AUSTRALIA HOLDINGS PTY LTD, HIGH RISK SOLUTIONS, XTREME ENGINEERING</t>
         </is>
       </c>
       <c r="X113" s="8" t="inlineStr">
@@ -26785,14 +26753,14 @@
           <t>SITE PLANT</t>
         </is>
       </c>
-      <c r="AU113" s="10" t="inlineStr">
-        <is>
-          <t>SITE PLANT</t>
-        </is>
-      </c>
-      <c r="AV113" s="10" t="inlineStr">
-        <is>
-          <t>SITE PLANT</t>
+      <c r="AU113" s="11" t="inlineStr">
+        <is>
+          <t>USED: CEMENT AUSTRALIA HOLDINGS PTY LTD</t>
+        </is>
+      </c>
+      <c r="AV113" s="9" t="inlineStr">
+        <is>
+          <t>OFF / NOT SEEN</t>
         </is>
       </c>
       <c r="AW113" s="8" t="inlineStr">
@@ -32205,7 +32173,7 @@
         <v>136.88</v>
       </c>
       <c r="R135" s="7" t="n">
-        <v>513.3</v>
+        <v>547.52</v>
       </c>
       <c r="S135" s="7" t="n">
         <v>34.22</v>
@@ -33186,20 +33154,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
       </c>
       <c r="L139" s="6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -33212,10 +33180,10 @@
         </is>
       </c>
       <c r="O139" s="7" t="n">
-        <v>791.1600000000001</v>
+        <v>527.4400000000001</v>
       </c>
       <c r="P139" s="7" t="n">
-        <v>1846.04</v>
+        <v>2109.76</v>
       </c>
       <c r="Q139" s="7" t="n">
         <v>2900.92</v>
@@ -33228,7 +33196,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>USED: TASMAN ROPE ACCESS</t>
+          <t>SITE PLANT</t>
         </is>
       </c>
       <c r="U139" t="n">
@@ -33239,7 +33207,7 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>DGH Engineering, TASMAN ROPE ACCESS</t>
+          <t>DGH Engineering</t>
         </is>
       </c>
       <c r="X139" s="8" t="inlineStr">
@@ -33362,9 +33330,9 @@
           <t>OFF / NOT SEEN</t>
         </is>
       </c>
-      <c r="AV139" s="11" t="inlineStr">
-        <is>
-          <t>USED: TASMAN ROPE ACCESS</t>
+      <c r="AV139" s="10" t="inlineStr">
+        <is>
+          <t>SITE PLANT</t>
         </is>
       </c>
       <c r="AW139" s="8" t="inlineStr">
@@ -34182,11 +34150,7 @@
           <t>INDIVIDUAL</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>On Hire</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>26/07/2026</t>
@@ -34229,7 +34193,7 @@
         <v>282.08</v>
       </c>
       <c r="R143" s="7" t="n">
-        <v>1057.8</v>
+        <v>1128.32</v>
       </c>
       <c r="S143" s="7" t="n">
         <v>70.52</v>
@@ -34694,20 +34658,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
       </c>
       <c r="L145" s="6" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -34720,23 +34684,23 @@
         </is>
       </c>
       <c r="O145" s="7" t="n">
-        <v>197.04</v>
+        <v>295.56</v>
       </c>
       <c r="P145" s="7" t="n">
-        <v>1477.8</v>
+        <v>1379.28</v>
       </c>
       <c r="Q145" s="7" t="n">
         <v>394.08</v>
       </c>
       <c r="R145" s="7" t="n">
-        <v>1477.8</v>
+        <v>1576.32</v>
       </c>
       <c r="S145" s="7" t="n">
         <v>98.52</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>SITE PLANT</t>
+          <t>USED: HIGH RISK SOLUTIONS</t>
         </is>
       </c>
       <c r="U145" t="n">
@@ -34870,9 +34834,9 @@
           <t>SITE PLANT</t>
         </is>
       </c>
-      <c r="AV145" s="10" t="inlineStr">
-        <is>
-          <t>SITE PLANT</t>
+      <c r="AV145" s="11" t="inlineStr">
+        <is>
+          <t>USED: HIGH RISK SOLUTIONS</t>
         </is>
       </c>
       <c r="AW145" s="8" t="inlineStr">
@@ -35217,7 +35181,7 @@
         <v>290.36</v>
       </c>
       <c r="R147" s="7" t="n">
-        <v>1088.85</v>
+        <v>1161.44</v>
       </c>
       <c r="S147" s="7" t="n">
         <v>72.59</v>
@@ -36188,7 +36152,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>On Hire</t>
+          <t>Available for Hire</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -39260,7 +39224,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Available for Hire</t>
+          <t>On Hire</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -39270,11 +39234,11 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J163" t="n">
         <v>2</v>
@@ -39283,7 +39247,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="6" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -39296,13 +39260,13 @@
         </is>
       </c>
       <c r="O163" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P163" s="7" t="n">
         <v>8</v>
       </c>
       <c r="Q163" s="7" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="R163" s="7" t="n">
         <v>8</v>
@@ -39312,7 +39276,7 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>OFF / NOT SEEN</t>
+          <t>USED: PROGRAMMED</t>
         </is>
       </c>
       <c r="U163" t="n">
@@ -39446,9 +39410,9 @@
           <t>OFF / NOT SEEN</t>
         </is>
       </c>
-      <c r="AV163" s="9" t="inlineStr">
-        <is>
-          <t>OFF / NOT SEEN</t>
+      <c r="AV163" s="11" t="inlineStr">
+        <is>
+          <t>USED: PROGRAMMED</t>
         </is>
       </c>
       <c r="AW163" s="8" t="inlineStr">
